--- a/nr-update-missing-fields/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T07:52:36+00:00</t>
+    <t>2024-07-17T09:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T09:13:15+00:00</t>
+    <t>2024-07-17T12:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -401,7 +401,7 @@
     <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
   </si>
   <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source.</t>
   </si>
   <si>
     <t>PractitionerRole.meta.versionId</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$80</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3000" uniqueCount="504">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:12:47+00:00</t>
+    <t>2024-07-17T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role-exercice</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -768,12 +768,30 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>PractitionerRole.identifier:idSituationExercice</t>
+  </si>
+  <si>
+    <t>idSituationExercice</t>
+  </si>
+  <si>
+    <t>Identifiant d'activité propre au RPPS</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.id</t>
+  </si>
+  <si>
     <t>PractitionerRole.identifier.id</t>
   </si>
   <si>
+    <t>PractitionerRole.identifier:idSituationExercice.extension</t>
+  </si>
+  <si>
     <t>PractitionerRole.identifier.extension</t>
   </si>
   <si>
+    <t>PractitionerRole.identifier:idSituationExercice.use</t>
+  </si>
+  <si>
     <t>PractitionerRole.identifier.use</t>
   </si>
   <si>
@@ -802,6 +820,9 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.type</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.type</t>
@@ -835,14 +856,16 @@
     <t>CX.5</t>
   </si>
   <si>
+    <t>PractitionerRole.identifier:idSituationExercice.system</t>
+  </si>
+  <si>
     <t>PractitionerRole.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value | Namespace du RASS)</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.
-Namespace du RASS)</t>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>Identifier.system is always case sensitive.</t>
@@ -851,6 +874,9 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>https://rpps.esante.gouv.fr</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
@@ -866,6 +892,9 @@
     <t>./IdentifierType</t>
   </si>
   <si>
+    <t>PractitionerRole.identifier:idSituationExercice.value</t>
+  </si>
+  <si>
     <t>PractitionerRole.identifier.value</t>
   </si>
   <si>
@@ -891,6 +920,9 @@
   </si>
   <si>
     <t>./Value</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.period</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.period</t>
@@ -906,9 +938,17 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
     <t>CX.7 + CX.8</t>
   </si>
   <si>
@@ -916,6 +956,9 @@
   </si>
   <si>
     <t>./StartDate and ./EndDate</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.assigner</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.assigner</t>
@@ -937,6 +980,10 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
@@ -944,42 +991,6 @@
   </si>
   <si>
     <t>./IdentifierIssuingAuthority</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice</t>
-  </si>
-  <si>
-    <t>idSituationExercice</t>
-  </si>
-  <si>
-    <t>Identifiant d'activité propre au RPPS</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.use</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.type</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.system</t>
-  </si>
-  <si>
-    <t>https://rpps.esante.gouv.fr</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.value</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.period</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.assigner</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:numeroAm</t>
@@ -1889,7 +1900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO88"/>
+  <dimension ref="A1:AO80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.21484375" customWidth="true" bestFit="true"/>
@@ -4866,9 +4877,11 @@
         <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4877,7 +4890,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4886,19 +4899,21 @@
         <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>104</v>
+        <v>230</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>105</v>
+        <v>242</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>106</v>
+        <v>232</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4946,53 +4961,53 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>107</v>
+        <v>229</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>108</v>
+        <v>237</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
@@ -5004,17 +5019,15 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5051,31 +5064,31 @@
         <v>78</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -5095,46 +5108,44 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>243</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>244</v>
+        <v>113</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5158,52 +5169,52 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>118</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5214,10 +5225,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5234,25 +5245,25 @@
         <v>78</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>253</v>
+        <v>175</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5277,13 +5288,13 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>157</v>
+        <v>253</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
@@ -5301,7 +5312,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5310,7 +5321,7 @@
         <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>102</v>
@@ -5319,10 +5330,10 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>261</v>
+        <v>198</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5333,10 +5344,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5359,19 +5370,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>137</v>
+        <v>260</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5384,43 +5395,43 @@
         <v>78</v>
       </c>
       <c r="T30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5429,7 +5440,7 @@
         <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>102</v>
@@ -5438,13 +5449,13 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>271</v>
+        <v>78</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>78</v>
@@ -5452,10 +5463,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5463,7 +5474,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>90</v>
@@ -5478,18 +5489,20 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N31" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5498,7 +5511,7 @@
         <v>78</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>276</v>
@@ -5546,7 +5559,7 @@
         <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>102</v>
@@ -5572,7 +5585,7 @@
         <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5595,7 +5608,7 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>282</v>
+        <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>283</v>
@@ -5603,7 +5616,9 @@
       <c r="M32" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="N32" s="2"/>
+      <c r="N32" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5616,7 +5631,7 @@
         <v>78</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>78</v>
+        <v>286</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>78</v>
@@ -5652,7 +5667,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5661,7 +5676,7 @@
         <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>102</v>
@@ -5670,13 +5685,13 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5684,10 +5699,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5710,16 +5725,16 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5769,7 +5784,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5778,22 +5793,22 @@
         <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>298</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -5801,14 +5816,12 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>78</v>
       </c>
@@ -5817,7 +5830,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>78</v>
@@ -5829,18 +5842,18 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>230</v>
+        <v>304</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
       </c>
@@ -5888,44 +5901,46 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>229</v>
+        <v>308</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>309</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>236</v>
+        <v>310</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>237</v>
+        <v>311</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>238</v>
+        <v>312</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>78</v>
       </c>
@@ -5934,7 +5949,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
@@ -5943,19 +5958,21 @@
         <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>104</v>
+        <v>230</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>105</v>
+        <v>315</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>106</v>
+        <v>232</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6003,53 +6020,53 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>107</v>
+        <v>229</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>78</v>
+        <v>316</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>108</v>
+        <v>237</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -6061,17 +6078,15 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6108,31 +6123,31 @@
         <v>78</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
@@ -6152,46 +6167,44 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>243</v>
+        <v>112</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>244</v>
+        <v>113</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6215,52 +6228,52 @@
         <v>78</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>250</v>
+        <v>118</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6271,10 +6284,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6291,25 +6304,25 @@
         <v>78</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>253</v>
+        <v>175</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6334,13 +6347,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>157</v>
+        <v>253</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -6358,7 +6371,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6367,7 +6380,7 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>102</v>
@@ -6376,10 +6389,10 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>261</v>
+        <v>198</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6390,10 +6403,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6401,7 +6414,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>90</v>
@@ -6416,19 +6429,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>137</v>
+        <v>260</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6438,46 +6451,46 @@
         <v>78</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>306</v>
+        <v>78</v>
       </c>
       <c r="T39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6486,7 +6499,7 @@
         <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>102</v>
@@ -6495,13 +6508,13 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>271</v>
+        <v>78</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>78</v>
@@ -6509,10 +6522,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6520,7 +6533,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>90</v>
@@ -6535,18 +6548,20 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N40" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
       </c>
@@ -6555,7 +6570,7 @@
         <v>78</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>78</v>
+        <v>322</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>276</v>
@@ -6603,7 +6618,7 @@
         <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>102</v>
@@ -6626,10 +6641,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6652,7 +6667,7 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>282</v>
+        <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>283</v>
@@ -6660,7 +6675,9 @@
       <c r="M41" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="N41" s="2"/>
+      <c r="N41" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -6673,7 +6690,7 @@
         <v>78</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>78</v>
+        <v>286</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>78</v>
@@ -6709,7 +6726,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6718,7 +6735,7 @@
         <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>102</v>
@@ -6727,13 +6744,13 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>78</v>
@@ -6741,10 +6758,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6767,16 +6784,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6826,7 +6843,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6835,22 +6852,22 @@
         <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>298</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -6858,14 +6875,12 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6874,7 +6889,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -6886,18 +6901,18 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>230</v>
+        <v>304</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6945,42 +6960,42 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>229</v>
+        <v>308</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>309</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>313</v>
+        <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>236</v>
+        <v>310</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>237</v>
+        <v>311</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>238</v>
+        <v>312</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>240</v>
+        <v>326</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6994,29 +7009,35 @@
         <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>104</v>
+        <v>327</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>105</v>
+        <v>328</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q44" s="2"/>
+      <c r="Q44" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="R44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7060,7 +7081,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>107</v>
+        <v>326</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7072,64 +7093,64 @@
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>78</v>
+        <v>333</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>108</v>
+        <v>334</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>78</v>
+        <v>335</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>241</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>111</v>
+        <v>293</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>112</v>
+        <v>337</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7165,54 +7186,54 @@
         <v>78</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>118</v>
+        <v>336</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>78</v>
+        <v>340</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>108</v>
+        <v>341</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>242</v>
+        <v>344</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7229,26 +7250,22 @@
         <v>78</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>175</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>243</v>
+        <v>105</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7272,13 +7289,13 @@
         <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -7296,7 +7313,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>250</v>
+        <v>107</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7308,16 +7325,16 @@
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>251</v>
+        <v>108</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7328,21 +7345,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>252</v>
+        <v>345</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>78</v>
@@ -7351,23 +7368,21 @@
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>253</v>
+        <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>254</v>
+        <v>112</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>255</v>
+        <v>113</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7391,52 +7406,52 @@
         <v>78</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>260</v>
+        <v>118</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7447,10 +7462,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>262</v>
+        <v>346</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7458,7 +7473,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
@@ -7473,20 +7488,18 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>137</v>
+        <v>347</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>263</v>
+        <v>348</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>264</v>
+        <v>349</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7495,10 +7508,10 @@
         <v>78</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>319</v>
+        <v>78</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>78</v>
@@ -7534,7 +7547,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>268</v>
+        <v>351</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7543,22 +7556,22 @@
         <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>78</v>
+        <v>352</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>78</v>
+        <v>353</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>269</v>
+        <v>354</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>270</v>
+        <v>355</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>271</v>
+        <v>78</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
@@ -7566,10 +7579,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>272</v>
+        <v>356</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7592,22 +7605,24 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>104</v>
+        <v>347</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>273</v>
+        <v>357</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>274</v>
+        <v>358</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>275</v>
+        <v>359</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q49" s="2"/>
+      <c r="Q49" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="R49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7615,7 +7630,7 @@
         <v>78</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>276</v>
+        <v>78</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>78</v>
@@ -7651,7 +7666,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>277</v>
+        <v>361</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7660,22 +7675,22 @@
         <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>78</v>
+        <v>352</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>78</v>
+        <v>362</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>278</v>
+        <v>363</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>279</v>
+        <v>364</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>280</v>
+        <v>78</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -7683,10 +7698,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>321</v>
+        <v>365</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>281</v>
+        <v>365</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7700,7 +7715,7 @@
         <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>78</v>
@@ -7709,13 +7724,13 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>282</v>
+        <v>366</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>283</v>
+        <v>367</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>284</v>
+        <v>368</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7766,7 +7781,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>285</v>
+        <v>365</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7784,13 +7799,13 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>286</v>
+        <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>287</v>
+        <v>369</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -7798,10 +7813,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>289</v>
+        <v>370</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7815,7 +7830,7 @@
         <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>78</v>
@@ -7824,17 +7839,15 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>290</v>
+        <v>371</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>291</v>
+        <v>372</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7883,7 +7896,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>294</v>
+        <v>370</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7901,13 +7914,13 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>295</v>
+        <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>296</v>
+        <v>374</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>78</v>
@@ -7915,10 +7928,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>323</v>
+        <v>375</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>323</v>
+        <v>375</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7929,10 +7942,10 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>78</v>
@@ -7941,26 +7954,24 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>324</v>
+        <v>260</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>325</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>326</v>
+        <v>377</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>327</v>
+        <v>378</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>328</v>
+        <v>379</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q52" t="s" s="2">
-        <v>329</v>
-      </c>
+      <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7980,37 +7991,33 @@
         <v>78</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>323</v>
+        <v>375</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>78</v>
@@ -8022,26 +8029,28 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>331</v>
+        <v>383</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>333</v>
+        <v>384</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8062,17 +8071,19 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>334</v>
+        <v>386</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>336</v>
+        <v>379</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8097,13 +8108,11 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>78</v>
+        <v>387</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8121,13 +8130,13 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>333</v>
+        <v>375</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>78</v>
@@ -8136,29 +8145,31 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>78</v>
+        <v>388</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>340</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>341</v>
+        <v>389</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="D54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8170,25 +8181,29 @@
         <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>104</v>
+        <v>260</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>105</v>
+        <v>391</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8212,13 +8227,11 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8236,31 +8249,31 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>107</v>
+        <v>375</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>78</v>
+        <v>393</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>108</v>
+        <v>383</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8268,44 +8281,48 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>342</v>
+        <v>394</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="D55" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>111</v>
+        <v>260</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>112</v>
+        <v>396</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>113</v>
+        <v>377</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8329,31 +8346,29 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>78</v>
+        <v>397</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>118</v>
+        <v>375</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8362,22 +8377,22 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>78</v>
+        <v>398</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>198</v>
+        <v>383</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8385,12 +8400,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>343</v>
+        <v>399</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8402,7 +8419,7 @@
         <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>78</v>
@@ -8411,18 +8428,20 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>344</v>
+        <v>260</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>345</v>
+        <v>401</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8446,13 +8465,11 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8470,31 +8487,31 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>349</v>
+        <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -8502,12 +8519,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>353</v>
+        <v>404</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8519,7 +8538,7 @@
         <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>78</v>
@@ -8528,24 +8547,24 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>344</v>
+        <v>260</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>354</v>
+        <v>406</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q57" t="s" s="2">
-        <v>357</v>
-      </c>
+      <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8565,13 +8584,11 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>78</v>
+        <v>407</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8589,31 +8606,31 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>349</v>
+        <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>359</v>
+        <v>408</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -8621,12 +8638,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>362</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="D58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8647,16 +8666,20 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>363</v>
+        <v>260</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>364</v>
+        <v>411</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8680,13 +8703,11 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8704,13 +8725,13 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>78</v>
@@ -8719,16 +8740,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>78</v>
@@ -8736,12 +8757,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>367</v>
+        <v>414</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
       </c>
@@ -8750,7 +8773,7 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>91</v>
@@ -8762,16 +8785,20 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>368</v>
+        <v>260</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>369</v>
+        <v>416</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -8795,13 +8822,11 @@
         <v>78</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>78</v>
+        <v>417</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -8819,13 +8844,13 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
@@ -8834,16 +8859,16 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>78</v>
+        <v>418</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -8851,10 +8876,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>372</v>
+        <v>419</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>372</v>
+        <v>419</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8877,20 +8902,16 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>373</v>
+        <v>420</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8914,27 +8935,29 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>179</v>
+        <v>253</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AC60" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>372</v>
+        <v>419</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8952,13 +8975,13 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>379</v>
+        <v>423</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>380</v>
+        <v>424</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>339</v>
+        <v>425</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -8966,14 +8989,12 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>381</v>
+        <v>426</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>78</v>
       </c>
@@ -8982,7 +9003,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>91</v>
@@ -8994,20 +9015,16 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>253</v>
+        <v>427</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>383</v>
+        <v>428</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9031,11 +9048,13 @@
         <v>78</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>78</v>
@@ -9053,7 +9072,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>372</v>
+        <v>426</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9068,31 +9087,29 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>379</v>
+        <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>380</v>
+        <v>430</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>339</v>
+        <v>431</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>78</v>
+        <v>432</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>386</v>
+        <v>433</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9101,7 +9118,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>91</v>
@@ -9110,23 +9127,19 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>253</v>
+        <v>434</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>388</v>
+        <v>435</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9150,11 +9163,13 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9172,7 +9187,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>372</v>
+        <v>433</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9187,16 +9202,16 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>390</v>
+        <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>379</v>
+        <v>437</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>380</v>
+        <v>438</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>78</v>
@@ -9204,14 +9219,12 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>391</v>
+        <v>439</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>78</v>
       </c>
@@ -9220,7 +9233,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>91</v>
@@ -9229,22 +9242,20 @@
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>253</v>
+        <v>440</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>393</v>
+        <v>441</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>376</v>
+        <v>443</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9269,29 +9280,29 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z63" t="s" s="2">
-        <v>394</v>
+        <v>78</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>372</v>
+        <v>439</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9300,22 +9311,22 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>445</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>395</v>
+        <v>446</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>379</v>
+        <v>447</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>380</v>
+        <v>448</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>339</v>
+        <v>449</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9323,13 +9334,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>396</v>
+        <v>450</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>372</v>
+        <v>439</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>397</v>
+        <v>451</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>78</v>
@@ -9339,31 +9350,29 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>253</v>
+        <v>452</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>398</v>
+        <v>453</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>376</v>
+        <v>443</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9388,11 +9397,13 @@
         <v>78</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>399</v>
+        <v>78</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>78</v>
@@ -9410,7 +9421,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>372</v>
+        <v>439</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9419,22 +9430,22 @@
         <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>445</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>400</v>
+        <v>454</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>379</v>
+        <v>447</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>380</v>
+        <v>448</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>339</v>
+        <v>449</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -9442,14 +9453,12 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>401</v>
+        <v>455</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9458,7 +9467,7 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>91</v>
@@ -9467,23 +9476,21 @@
         <v>78</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>253</v>
+        <v>456</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>374</v>
+        <v>458</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9507,11 +9514,13 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9529,7 +9538,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>372</v>
+        <v>455</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9544,16 +9553,16 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>405</v>
+        <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>379</v>
+        <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>380</v>
+        <v>460</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -9561,14 +9570,12 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>406</v>
+        <v>461</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9580,29 +9587,25 @@
         <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>408</v>
+        <v>105</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9626,11 +9629,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z66" t="s" s="2">
-        <v>409</v>
+        <v>78</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9648,31 +9653,31 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>372</v>
+        <v>107</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>410</v>
+        <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>379</v>
+        <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>380</v>
+        <v>108</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -9680,16 +9685,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>411</v>
+        <v>462</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9699,29 +9702,27 @@
         <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>253</v>
+        <v>111</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>413</v>
+        <v>112</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>374</v>
+        <v>113</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
       </c>
@@ -9745,11 +9746,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>414</v>
+        <v>78</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9767,7 +9770,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>372</v>
+        <v>118</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9779,19 +9782,19 @@
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>379</v>
+        <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>380</v>
+        <v>108</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -9799,14 +9802,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>416</v>
+        <v>463</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>416</v>
+        <v>463</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>78</v>
+        <v>464</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9819,22 +9822,26 @@
         <v>78</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>253</v>
+        <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
@@ -9858,11 +9865,13 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>419</v>
+        <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -9880,7 +9889,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>416</v>
+        <v>467</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9892,19 +9901,19 @@
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>421</v>
+        <v>198</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>422</v>
+        <v>78</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9912,10 +9921,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9929,22 +9938,22 @@
         <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>424</v>
+        <v>175</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>426</v>
+        <v>470</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9971,13 +9980,13 @@
         <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>78</v>
+        <v>253</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>78</v>
+        <v>471</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>78</v>
+        <v>472</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -9995,7 +10004,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10016,21 +10025,21 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>427</v>
+        <v>460</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>428</v>
+        <v>78</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>429</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>430</v>
+        <v>473</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>430</v>
+        <v>473</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10041,10 +10050,10 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>78</v>
@@ -10053,13 +10062,13 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>431</v>
+        <v>327</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>432</v>
+        <v>474</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>433</v>
+        <v>475</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10110,13 +10119,13 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>430</v>
+        <v>473</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>78</v>
@@ -10128,10 +10137,10 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>434</v>
+        <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -10142,10 +10151,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10156,10 +10165,10 @@
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>78</v>
@@ -10168,18 +10177,18 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>437</v>
+        <v>477</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>438</v>
+        <v>478</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10215,41 +10224,43 @@
         <v>78</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AC71" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>442</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>443</v>
+        <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>444</v>
+        <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>446</v>
+        <v>78</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10257,14 +10268,12 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>447</v>
+        <v>481</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10273,7 +10282,7 @@
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -10285,18 +10294,18 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>450</v>
+        <v>482</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10344,31 +10353,31 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>436</v>
+        <v>481</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>442</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>451</v>
+        <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>444</v>
+        <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>446</v>
+        <v>78</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10376,10 +10385,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>452</v>
+        <v>484</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>452</v>
+        <v>484</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10402,17 +10411,15 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10461,7 +10468,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>452</v>
+        <v>484</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10482,7 +10489,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10493,10 +10500,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>458</v>
+        <v>487</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>458</v>
+        <v>487</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10608,10 +10615,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>459</v>
+        <v>488</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>459</v>
+        <v>488</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10725,14 +10732,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>460</v>
+        <v>489</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>460</v>
+        <v>489</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10754,10 +10761,10 @@
         <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>114</v>
@@ -10812,7 +10819,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10844,10 +10851,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10855,10 +10862,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
@@ -10870,13 +10877,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>175</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10903,13 +10910,13 @@
         <v>78</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>468</v>
+        <v>78</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>469</v>
+        <v>78</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>78</v>
@@ -10927,13 +10934,13 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>78</v>
@@ -10948,7 +10955,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>457</v>
+        <v>108</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10959,10 +10966,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10985,13 +10992,13 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>324</v>
+        <v>293</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11042,7 +11049,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11063,7 +11070,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11074,10 +11081,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11091,7 +11098,7 @@
         <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>78</v>
@@ -11100,17 +11107,15 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>474</v>
+        <v>104</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11159,7 +11164,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11180,7 +11185,7 @@
         <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11191,10 +11196,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11205,10 +11210,10 @@
         <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>78</v>
@@ -11217,18 +11222,18 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
@@ -11276,13 +11281,13 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>78</v>
@@ -11297,945 +11302,17 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>457</v>
+        <v>108</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO88" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO88">
+  <autoFilter ref="A1:AO80">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12245,7 +11322,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI87">
+  <conditionalFormatting sqref="A2:AI79">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:12:21+00:00</t>
+    <t>2024-07-25T07:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
